--- a/docs/htr/golden_truth.xlsx
+++ b/docs/htr/golden_truth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugenia/Desktop/thesis/magic_tagger/docs/htr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA42C09D-06DE-9D46-9ADA-3EF64155CF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C332912-708A-4347-9490-EF2EE18FABA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -853,18 +853,20 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="3" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" customWidth="1"/>
+    <col min="4" max="5" width="18" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="20" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="24" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="17.5" customWidth="1"/>
-    <col min="11" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="19" width="14" customWidth="1"/>
+    <col min="15" max="15" width="14" hidden="1" customWidth="1"/>
+    <col min="16" max="19" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="47" customHeight="1" x14ac:dyDescent="0.2">
@@ -1122,7 +1124,7 @@
         <v>0.5641025641025641</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>84</v>
       </c>
